--- a/ewatch_data/meter_export_cons_gen.xlsx
+++ b/ewatch_data/meter_export_cons_gen.xlsx
@@ -25,7 +25,7 @@
     <t>Parameter: Abs Active Energy (kWh)</t>
   </si>
   <si>
-    <t xml:space="preserve">Duration(dd/mm/yyyy): 04/06/2026 </t>
+    <t xml:space="preserve">Duration(dd/mm/yyyy): 08/06/2026 </t>
   </si>
   <si>
     <t>INSTITUTIONAL Area</t>
@@ -412,17 +412,17 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B3">
-        <v>11989</v>
+        <v>13113</v>
       </c>
       <c r="C3">
-        <v>9429</v>
+        <v>9974.5</v>
       </c>
       <c r="D3" s="1">
         <f>SUM(B3:C3)</f>
-        <v>21418</v>
+        <v>23087.5</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="1" customFormat="1">
@@ -431,15 +431,15 @@
       </c>
       <c r="B4" s="1">
         <f>SUM(B3:B3)</f>
-        <v>11989</v>
+        <v>13113</v>
       </c>
       <c r="C4" s="1">
         <f>SUM(C3:C3)</f>
-        <v>9429</v>
+        <v>9974.5</v>
       </c>
       <c r="D4" s="1">
         <f>SUM(B4:C4)</f>
-        <v>21418</v>
+        <v>23087.5</v>
       </c>
     </row>
   </sheetData>
@@ -447,7 +447,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LNote : Blank column/s = data unavailable 
- Printed Date : 05/06/2026 06:23:26 PM 
+ Printed Date : 09/06/2026 01:35:07 PM 
  Daily meter reading will be the first reading of the day where meter is successfully connected.</oddFooter>
   </headerFooter>
 </worksheet>
